--- a/jupyter/dataloader/templates/Employee_Master_Dynamic_statea.xlsx
+++ b/jupyter/dataloader/templates/Employee_Master_Dynamic_statea.xlsx
@@ -967,7 +967,7 @@
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>An error occurred while accessing a underlying resource</t>
+          <t>User creation failed at the user service.</t>
         </is>
       </c>
     </row>
